--- a/05_Figures/F06_prediction/proteins/T1/d_1rm_ext/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T1/d_1rm_ext/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -128,21 +128,21 @@
     <t xml:space="preserve">freq</t>
   </si>
   <si>
+    <t xml:space="preserve">ROMO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCARB2</t>
+  </si>
+  <si>
     <t xml:space="preserve">MSRB2</t>
   </si>
   <si>
+    <t xml:space="preserve">NDUFA4</t>
+  </si>
+  <si>
     <t xml:space="preserve">RASA4</t>
   </si>
   <si>
-    <t xml:space="preserve">ROMO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCARB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFA4</t>
-  </si>
-  <si>
     <t xml:space="preserve">ERGIC1</t>
   </si>
   <si>
@@ -152,400 +152,421 @@
     <t xml:space="preserve">MOGS</t>
   </si>
   <si>
+    <t xml:space="preserve">AHSA1</t>
+  </si>
+  <si>
     <t xml:space="preserve">ATP6V1B2</t>
   </si>
   <si>
-    <t xml:space="preserve">AHSA1</t>
+    <t xml:space="preserve">CAV1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS16</t>
   </si>
   <si>
     <t xml:space="preserve">ALDH7A1</t>
   </si>
   <si>
-    <t xml:space="preserve">CAV1</t>
+    <t xml:space="preserve">CBR4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBKS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDHD5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFAB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHMT1</t>
   </si>
   <si>
     <t xml:space="preserve">SRM</t>
   </si>
   <si>
-    <t xml:space="preserve">CBR4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HDHD5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFAB1</t>
+    <t xml:space="preserve">ATP5F1C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPS2</t>
   </si>
   <si>
     <t xml:space="preserve">NONO</t>
   </si>
   <si>
+    <t xml:space="preserve">OGDH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIC5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GATD3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCTS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MGLL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEK7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMA5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBE2D3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5MF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDV3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHD4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRGQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTX2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDHB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PKLR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RWDD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIMM10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UFM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACADS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADSS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHCYL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKR1C2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARHGAP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP1A1</t>
+  </si>
+  <si>
     <t xml:space="preserve">CA14</t>
   </si>
   <si>
-    <t xml:space="preserve">COPS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EHD4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OGDH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5F1C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GATD3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCTS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPS16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEK7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMA5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RWDD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHMT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPRKB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBE2D3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5MF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDV3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIC5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPHN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRGQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCBP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDHB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKLR</t>
+    <t xml:space="preserve">CALM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHCHD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CKM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CKMT1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPS8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COQ10A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSRP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DBI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCUN1D1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDAH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDX39B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEPTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUSP28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUSP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECHS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF1G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF2S1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF4E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENDOD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESYT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GHITM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLRX5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H6PD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INPP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISOC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LANCL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LRRC20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP2K4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAT2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MT-CYB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFA9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFB7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIF3L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NLN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NXN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLIN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP2CB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP2R2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRDX1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMA6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMA7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMB1</t>
   </si>
   <si>
     <t xml:space="preserve">PTBP1</t>
   </si>
   <si>
+    <t xml:space="preserve">PTGES3</t>
+  </si>
+  <si>
     <t xml:space="preserve">QDPR</t>
   </si>
   <si>
-    <t xml:space="preserve">RBKS</t>
+    <t xml:space="preserve">RAB8A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RARS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCSD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEC22B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNTA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPTAN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STXBP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUCLG2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIMM50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMX3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TNPO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRMT10C</t>
   </si>
   <si>
     <t xml:space="preserve">TRMT112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UFM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABCB7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACADS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHCYL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AK2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP1A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CALM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CALR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMK2D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHCHD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CKM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CKMT1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPS8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COQ10A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSRP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DBI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCUN1D1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDAH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDX39B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEPTOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUSP28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUSP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEF1G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EHD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF2S1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF4E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENDOD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESYT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GHITM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLRX5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H6PD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOOK3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INPP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISOC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LRRC20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP2K4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAT2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MGLL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOCS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPS36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MT-CYB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTX2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFA9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFB7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NIF3L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NLN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NXN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAK2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLIN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP2CB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP2R2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRDX1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMA6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMA7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTGES3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB8A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RCSD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC22B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SGCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNTA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPTAN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STAT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STXBP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUCLG2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIMM21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMX3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TNPO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRMT10C</t>
   </si>
   <si>
     <t xml:space="preserve">TUBB4B</t>
@@ -944,16 +965,16 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0326438019885298</v>
+        <v>-0.177213966250994</v>
       </c>
       <c r="I2" t="n">
-        <v>0.381058193101592</v>
+        <v>0.167401287142896</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -977,29 +998,21 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0326438019885298</v>
+        <v>-0.177213966250994</v>
       </c>
       <c r="I3" t="n">
-        <v>0.381058193101592</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.134328358208955</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.109452736318408</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.711545896937507</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.644108020947732</v>
-      </c>
+        <v>0.167401287142896</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1023,2206 +1036,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.182091344476498</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-1.30005000507456</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-1.22517628289461</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-2.18115881274166</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.552963268758598</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.344842298780022</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-1.76520407158907</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.635489697313973</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.6092789747365</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.256533754639168</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-1.22792797203556</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.419619245255087</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.245504550059844</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-1.72980758156116</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.840027235151187</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.90408308219509</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-1.76105595510208</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.22643806524568</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-0.838932917876114</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-0.594600197902939</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.114628605044665</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-2.72551708981203</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-0.714058980467406</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.666959359184143</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-0.552230908058505</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-1.15748002144051</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-0.0403092411595658</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-1.69079512890714</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.915682151369277</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-1.26654950813559</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-0.58632026747676</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-0.33117568460392</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-1.09007589627427</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-1.08754106284458</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-1.69048038191814</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-0.605005024685261</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-1.29819724470748</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-0.978033702306769</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.248962471186105</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.644597302598694</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-0.501368621128677</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-0.0188050465572858</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-0.542785603083641</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.642200285764277</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0.30152944808588</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-0.801815065016472</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.927944292309803</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.161992821601043</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-1.00039957443072</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.152890256744536</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.638644731032125</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-0.0326105981747065</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.583950391578549</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-1.51266291251617</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-0.0778170924963473</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-1.19417993206468</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-1.57973636284719</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-0.514619197588581</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-0.849801923736251</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.00730004687834862</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-0.697646517595381</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-0.418888588904278</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-1.72468649369714</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-0.980159406509017</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-1.14679565463313</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-0.10070457516796</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-0.570176414013485</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-0.46521932303887</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-0.670593773682617</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0.241274757539239</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-0.674159139095329</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>0.16011465064311</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-2.21329115129304</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-0.636857307855363</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-0.769327403071279</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-1.36114995160972</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-0.276691592060626</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>0.329923405699476</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-1.05254847132131</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-2.20357269571207</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-0.532702894780434</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-0.385879231449574</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-0.267917706888471</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-0.0846835158781032</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-0.0672190184140455</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-0.356169854773456</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-1.75502596994941</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-0.318600988051956</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-1.27818249437908</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-0.358660880546205</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-0.0764949322095465</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-1.14543843251143</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>0.0222255323885938</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-1.05347823254177</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-1.2754171639645</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-2.61315247210888</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-0.982749674474904</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-0.501355233948195</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-1.07250958322056</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-0.926303790169812</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-0.402748380870576</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-0.328896437968788</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.819717261975682</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-0.333829977856348</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-1.87804906228196</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-1.74841311673822</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-0.709181781323697</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.830196746309563</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-1.1864054434528</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>0.482226980621979</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-0.647799129429119</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-0.789674074759752</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-1.09471478875579</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-0.305659172618435</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-2.24816902881563</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-0.518959903613619</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-0.771396235623199</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-1.1684381469835</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-1.53379859756079</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-0.964651879289626</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-0.256747909212399</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-0.610524214292543</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-1.47372258923622</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-0.849619922053272</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-0.540373485062047</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-0.545268870632861</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.32654972216074</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-0.483923558826557</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-0.636584416175602</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-1.27891201252686</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-0.28237704403281</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.802786145031741</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-0.447883064039035</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-0.347764918419698</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>0.170207309587777</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>0.602231144425908</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-0.83165899337261</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-1.2235698654021</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-0.789503781807994</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-1.39309118426094</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-0.221372030441613</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-0.136387213279599</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-0.518960380210311</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.535029553282218</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>0.159735587414413</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-2.62495048859713</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-0.579071873427447</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-1.46651444798319</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-0.395092660187874</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.0630658862131519</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-2.10185861348502</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-1.08471329103817</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-1.06976695876465</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-0.954933712413029</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-1.02978730937325</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-1.26174419591072</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>0.777756270223821</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-0.214022101601257</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-2.091427137932</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-1.63439003917078</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-0.201264521391242</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.996951772230834</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.799386410276785</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-0.695568528090636</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.692931639567185</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-0.418095512457878</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.976922403981867</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-0.752409134324727</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>0.182669022981746</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-0.649946783308564</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>0.041272675134001</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-1.26235320719992</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-0.780668984079266</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.00614293082439699</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-0.874867245095508</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.28542470360042</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>0.431807743531782</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-0.850297589728632</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>-0.502185956731145</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>0.204377121920646</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-0.318678802354835</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-1.40436622234649</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>0.265878403858871</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>-0.869641634033367</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-0.252742518628259</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-0.217738420449786</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-0.312502393645907</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>0.620442997550288</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-0.614968157664792</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>-0.440596928120713</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-1.77539192318334</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-0.0169670749414177</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-0.0374636902935148</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>0.228456949431324</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>0.336395221151528</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-1.45182554573758</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>0.222771294870294</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-0.774953402778613</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-0.347713527403654</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-0.716978852408105</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3265,7 +1078,7 @@
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>5.10320597360041</v>
+        <v>4.43529848915763</v>
       </c>
     </row>
     <row r="3">
@@ -3282,7 +1095,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>8.42883141865916</v>
+        <v>8.45831311939466</v>
       </c>
     </row>
     <row r="4">
@@ -3299,7 +1112,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>13.4630186157734</v>
+        <v>13.6462908428879</v>
       </c>
     </row>
     <row r="5">
@@ -3316,7 +1129,7 @@
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>6.92836394349283</v>
+        <v>7.34291102382203</v>
       </c>
     </row>
     <row r="6">
@@ -3333,7 +1146,7 @@
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>13.7794632409332</v>
+        <v>12.7684590118378</v>
       </c>
     </row>
     <row r="7">
@@ -3350,7 +1163,7 @@
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>6.32803002054378</v>
+        <v>6.42425446782183</v>
       </c>
     </row>
     <row r="8">
@@ -3367,7 +1180,7 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>11.6878678958335</v>
+        <v>12.1656572282403</v>
       </c>
     </row>
     <row r="9">
@@ -3384,7 +1197,7 @@
         <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>10.1051350847778</v>
+        <v>9.79970877502087</v>
       </c>
     </row>
     <row r="10">
@@ -3401,7 +1214,7 @@
         <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>7.91460913437445</v>
+        <v>8.76388484796523</v>
       </c>
     </row>
     <row r="11">
@@ -3418,7 +1231,7 @@
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>7.17812942846035</v>
+        <v>7.86487907472021</v>
       </c>
     </row>
     <row r="12">
@@ -3435,7 +1248,7 @@
         <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>9.20107372325453</v>
+        <v>7.63684948001238</v>
       </c>
     </row>
     <row r="13">
@@ -3452,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>6.22940212621554</v>
+        <v>6.64429476396326</v>
       </c>
     </row>
     <row r="14">
@@ -3469,7 +1282,7 @@
         <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>7.08034164070776</v>
+        <v>5.85481715120671</v>
       </c>
     </row>
     <row r="15">
@@ -3486,7 +1299,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3178052847694</v>
+        <v>5.67166246106779</v>
       </c>
     </row>
   </sheetData>
@@ -3562,10 +1375,10 @@
         <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="5">
@@ -3579,10 +1392,10 @@
         <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="6">
@@ -3596,10 +1409,10 @@
         <v>41</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>0.857142857142857</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="7">
@@ -3613,10 +1426,10 @@
         <v>42</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0.714285714285714</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="8">
@@ -3630,10 +1443,10 @@
         <v>43</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0.714285714285714</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="9">
@@ -3681,10 +1494,10 @@
         <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="12">
@@ -3698,10 +1511,10 @@
         <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="13">
@@ -3715,10 +1528,10 @@
         <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="14">
@@ -3749,10 +1562,10 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>0.428571428571429</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16">
@@ -3766,10 +1579,10 @@
         <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>0.357142857142857</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="17">
@@ -3817,10 +1630,10 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>0.285714285714286</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="20">
@@ -3834,10 +1647,10 @@
         <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>0.285714285714286</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="21">
@@ -3851,10 +1664,10 @@
         <v>56</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>0.285714285714286</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="22">
@@ -3902,10 +1715,10 @@
         <v>59</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>0.214285714285714</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="25">
@@ -3919,10 +1732,10 @@
         <v>60</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>0.214285714285714</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="26">
@@ -4089,10 +1902,10 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="36">
@@ -4327,10 +2140,10 @@
         <v>84</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="50">
@@ -4344,10 +2157,10 @@
         <v>85</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="51">
@@ -5962,6 +3775,125 @@
         <v>1</v>
       </c>
       <c r="E145" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="s">
+        <v>181</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="s">
+        <v>182</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="s">
+        <v>183</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="s">
+        <v>184</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="s">
+        <v>185</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="s">
+        <v>186</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="s">
+        <v>187</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="n">
         <v>0.0714285714285714</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/T1/d_1rm_ext/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T1/d_1rm_ext/spls/c_data/results.xlsx
@@ -1001,7 +1001,7 @@
         <v>1898</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.177213966250994</v>
@@ -1009,10 +1009,18 @@
       <c r="I3" t="n">
         <v>0.167401287142896</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.199004975124378</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.213930348258706</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.71055321139253</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.66959024293235</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1036,6 +1044,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.00106613412461565</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.11612129493438</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.21616825114798</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-2.07348075420386</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.446746130488549</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.257396765079497</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.07021758744212</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.586082963931833</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.672262190737599</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.186148530386209</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.851184886047346</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.354095213440126</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.153795658300626</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-1.55275687733812</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.794315469789714</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-1.0177151127755</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-1.84806200505897</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.122758521930681</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.0209867338330703</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.11108057549449</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.124359689332737</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-2.76923918281466</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.448249201626528</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.81637690496198</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.514858779584789</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-1.30635263327268</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.000187076017460486</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-1.4799824630435</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.848886663370575</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-1.30492746174383</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.731637925493268</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.279637964478748</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-1.17955072791616</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.952992117536903</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-2.07754012561694</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.836550267494891</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-1.39172718201898</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-1.09450971663389</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.37549023864225</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.62148472511355</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.468089697713318</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.0759545904891814</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.891569858772294</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.50797154132472</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.269973740538518</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.757626890554611</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.803690264670117</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.110369538778717</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.8103940465384</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.0219522914677377</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.633187083114093</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.0368412162656726</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.766052501671429</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-1.510505565569</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.370081151365981</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-1.08347954105703</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-1.35495402087389</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.43862329191593</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.775267919450407</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.162905476241461</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.436350036879734</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.36948097375945</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-1.76520983790753</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-1.08583425241817</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.791340808138257</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.248140026039411</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.740997997103114</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.401466535028263</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.577771228890791</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.170766449607483</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-1.09349988579888</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.135012513872258</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-4.09180746230815</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.713532331141314</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-0.780650950726881</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-1.65911654222499</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.563438576804022</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.392051014827317</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-1.47850460359767</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-0.734626996923062</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.511013743148698</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.495397505929477</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.258264857685968</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.106004510455853</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.0799440113838166</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.503586708481195</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-1.64868367087696</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.305225514497191</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-1.67376556602051</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-0.506940715558647</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.0253633089922856</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-1.6334342905096</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.256183964382016</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-1.1621251117511</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-1.47809510930314</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-1.69151894563864</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-1.05344324509497</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.476399085531718</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-0.536608013355166</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.718197759046438</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-0.649153979100239</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.206117146371229</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.733148405638827</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.1003726785283</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-1.42709567086427</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-1.58775086192159</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.690775697171482</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-1.00352259250206</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.984617895524149</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0.452391755163777</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.84248569440577</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.799393349417053</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.870599563544432</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.301195693085356</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-2.24664044336451</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-0.389912616133453</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.24335495091054</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-1.30334964257048</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-1.2876989637263</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.970045596237981</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.676460202286074</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-0.582583819999283</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-2.46216247358821</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.577604888501739</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.662232269871518</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.520046399526904</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.394399968579253</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.416741167980096</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.545158162083354</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-1.62953955248778</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-0.564199959587225</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.765886332750985</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.492217798646599</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-0.730563503891607</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.415215357265017</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.58721174892046</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.913608259410495</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.919854075403816</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-0.895767070339861</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-1.16189022483832</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.10633070318949</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.207857880876242</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-0.60058815325575</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.584738917014534</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0.254869297916431</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-2.59731565538706</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-0.561974166530424</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-1.6877695589099</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.432599061326834</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0.0897187484995133</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-1.47502389874921</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.981585815037325</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.879635924700612</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.839547404998807</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-0.951936373496828</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-1.49500132133887</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>0.829176811785651</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-0.279621329556958</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.903501438686626</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-1.9279447312819</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-0.218971230024123</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.98603899523618</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.982001471421826</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.601966623352421</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.631049187542083</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.49349539777709</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-1.0453126488467</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.319822456287506</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0.258385123760275</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.842192857776601</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-0.21581966137234</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-1.0619535155377</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-0.970577370625985</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.0457121168896675</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-0.977922255904975</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.122993273351669</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.404778890176627</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-0.818761968418062</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-0.300879457798663</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.199664425866294</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-0.388541715050578</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-2.30542590589214</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-0.0404375043968423</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-0.682216344456863</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-0.196248586661554</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.131164532272426</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.418792709232344</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0.621110496889024</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-0.750597608064053</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-0.326710389687954</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-1.87421333796271</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0.0228536225044217</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.0904271336914544</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0.126761835872044</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0.318220321414893</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-1.38555927292347</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0.340126187724465</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-0.903311287781418</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.341959559603118</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.833354848262186</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
